--- a/influencer_forms/028_influencer_partnership_verification_form--influencer_forms.xlsx
+++ b/influencer_forms/028_influencer_partnership_verification_form--influencer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>partnership_details</t>
+          <t>Partnership Details</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,14 +548,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>brand_partnership_preferences</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Select one</t>
-        </is>
-      </c>
+          <t>Brand Partnership Type</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -575,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>audience_characteristics</t>
+          <t>Audience Characteristics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -598,36 +594,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>Contact Info</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>brand_requirements</t>
+          <t>verification_documents</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>brand_requirements</t>
+          <t>Verification Documents</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>partnership_history</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>partnership_history</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,24 +653,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>verification_documents</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>verification_documents</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -689,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>additional_notes</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>additional_notes</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -712,22 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>your email@example.com</t>
-        </is>
-      </c>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -739,22 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>number_of_streams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>123-456-7890</t>
-        </is>
-      </c>
+          <t>Number of Streams</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -766,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>stream_url</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Stream URL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -789,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>discord_server</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>Discord Server</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -812,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>discord_username</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>Discord Username</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -835,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>pinterest_channel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>Pinterest Channel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -858,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>pinterest_profile_url</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>Pinterest Profile URL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -881,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pinterest</t>
+          <t>pinterest_board</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pinterest</t>
+          <t>Pinterest Board</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>twitch_twitch_streams</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>Twitch/Twitch Streams</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -927,18 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>discord</t>
+          <t>snapchat_channel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>discord</t>
+          <t>Snapchat Channel</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -950,18 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>snapchat_stream_url</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>Snapchat Stream URL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -973,18 +957,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>youtube_channel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>YouTube Channel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -996,18 +980,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>twitch</t>
+          <t>youtube_stream_url</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>twitch</t>
+          <t>YouTube Stream URL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1019,865 +1003,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>twitch_channel</t>
+          <t>youtube_streams</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>twitch_channel</t>
+          <t>YouTube Streams</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>twitch_username</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>twitch_username</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>twitch_stream_url</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>twitch_stream_url</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>twitch_streams</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>twitch_streams</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>How many streams</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>tiktok_channel</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>tiktok_channel</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>tiktok_stream_url</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>tiktok_stream_url</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>tiktok_streams</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>tiktok_streams</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>How many streams</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>youtube_channel</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>youtube_channel</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>youtube_stream_url</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>youtube_stream_url</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>youtube_streams</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>youtube_streams</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>How many streams</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>instagram_channel</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>instagram_channel</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>instagram_stream_url</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>instagram_stream_url</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>instagram_streams</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>instagram_streams</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>How many streams</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>snapchat_channel</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>snapchat_channel</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>snapchat_stream_url</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>snapchat_stream_url</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>snapchat_streams</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>snapchat_streams</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>How many streams</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>twitch_twitch_streams</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>twitch_twitch_streams</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Twitch/Twitch Streams</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>discord_server</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>discord_server</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>discord_username</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>discord_username</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>discord_tag</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>discord_tag</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>twitter_channel</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>twitter_channel</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>twitter_username</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>twitter_username</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>tiktok_channel</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>tiktok_channel</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>tiktok_stream_url</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>tiktok_stream_url</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>instagram_channel</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>instagram_channel</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>instagram_tag</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>instagram_tag</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>pinterest_channel</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>pinterest_channel</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>pinterest_board</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>pinterest_board</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Pinterest Board</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>pinterest_profile_url</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>pinterest_profile_url</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Pinterest Profile URL</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>discord_channel</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>discord_channel</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>youtube_channel</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>youtube_channel</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>youtube_tag</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>youtube_tag</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>tiktok_profile_url</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>tiktok_profile_url</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TikTok Profile URL</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>snapchat_profile_url</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>snapchat_profile_url</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>your snapchat.com/username</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>youtube_profile_url</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>youtube_profile_url</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>your channel.com/username</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1894,12 +1029,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1927,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'partner_as_a_brand'}</t>
+          <t>partner_as_a_brand</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Partner as a brand'}</t>
+          <t>Partner as a brand</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'partner_as_a_content_creator'}</t>
+          <t>partner_as_a_content_creator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Partner as a content creator'}</t>
+          <t>Partner as a content creator</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tiktok'}</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'TikTok'}</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -2012,12 +1147,97 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'twitch'}</t>
+          <t>twitch</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Twitch'}</t>
+          <t>Twitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>verification_documents_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>twitter</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Twitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>verification_documents_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>verification_documents_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>discord</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Discord</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>verification_documents_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>verification_documents_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>snapchat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Snapchat</t>
         </is>
       </c>
     </row>
